--- a/FASE 3/Documentacion del proyecto/Planilla Registro de Defectos.xlsx
+++ b/FASE 3/Documentacion del proyecto/Planilla Registro de Defectos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeanette Leonelli\Desktop\2024-2\PTY4614\Fase3 - Presentacion del proyecto\DocumentosFase3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GAMER\CAPSTONE-PPY4614-007D\FASE 3\Documentacion del proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371146AC-1F03-49FB-85C5-F620390EFE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF54C626-A64B-46D2-BC8D-C7D1F170497E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14280" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Defectos" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="78">
   <si>
     <t>ID</t>
   </si>
@@ -44,12 +44,6 @@
     <t>Jefe proyecto</t>
   </si>
   <si>
-    <t>Analista Testing</t>
-  </si>
-  <si>
-    <t>Desarrollador</t>
-  </si>
-  <si>
     <t>Fecha</t>
   </si>
   <si>
@@ -132,13 +126,145 @@
   </si>
   <si>
     <t>REGISTRO DE DEFECTOS DEL SISTEMA</t>
+  </si>
+  <si>
+    <t>Mi Refugio</t>
+  </si>
+  <si>
+    <t>Mateo Flores</t>
+  </si>
+  <si>
+    <t>Jefe de desarrollo</t>
+  </si>
+  <si>
+    <t>Analista QA</t>
+  </si>
+  <si>
+    <t>Arquitecto de Software</t>
+  </si>
+  <si>
+    <t>Pierre Salas</t>
+  </si>
+  <si>
+    <t>Matias Rubilar</t>
+  </si>
+  <si>
+    <t>Isaías Veloz</t>
+  </si>
+  <si>
+    <t>D-01</t>
+  </si>
+  <si>
+    <t>D-02</t>
+  </si>
+  <si>
+    <t>D-03</t>
+  </si>
+  <si>
+    <t>D-04</t>
+  </si>
+  <si>
+    <t>D-05</t>
+  </si>
+  <si>
+    <t>D-06</t>
+  </si>
+  <si>
+    <t>D-07</t>
+  </si>
+  <si>
+    <t>D-08</t>
+  </si>
+  <si>
+    <t>D-09</t>
+  </si>
+  <si>
+    <t>Error al conectar API a AWS RDS PostgreSQL en ambiente de pruebas; la app no podía guardar registros emocionales.</t>
+  </si>
+  <si>
+    <t>Se corrigió la cadena de conexión y las variables de entorno; la API ahora opera correctamente y sincroniza datos.</t>
+  </si>
+  <si>
+    <t>Backend - API / Conexión BD</t>
+  </si>
+  <si>
+    <t>web</t>
+  </si>
+  <si>
+    <t>app móvil</t>
+  </si>
+  <si>
+    <t>base de datos</t>
+  </si>
+  <si>
+    <t>web / formulario</t>
+  </si>
+  <si>
+    <t>Machine learning</t>
+  </si>
+  <si>
+    <t>seguridad</t>
+  </si>
+  <si>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>Se ejecutaron migraciones y se configuraron correctamente las variables; el servicio opera con normalidad.</t>
+  </si>
+  <si>
+    <t>La plataforma web desplegada en Render mostraba error 500 al cargar la vista de login debido a migraciones pendientes y variables de entorno mal configuradas.</t>
+  </si>
+  <si>
+    <t>La aplicaciómm se cerraba al registrar una emoción cuando el campo "comentario" era enviado vacio</t>
+  </si>
+  <si>
+    <t>Se corrigió la validación del formulario y se añadió control de valores nulos tanto en la app como en la API.</t>
+  </si>
+  <si>
+    <t>Se encontraron registros en emotion_logs con user_id inexistente en la tabla users durante pruebas de integración.</t>
+  </si>
+  <si>
+    <t>Se depuraron registros inválidos, se reforzó la FK y se ajustó el flujo de inserción desde el backend.</t>
+  </si>
+  <si>
+    <t>El historial emocional mostraba registros duplicados tras refrescar repetidamente la vista.</t>
+  </si>
+  <si>
+    <t>Se resetea la lista antes de recargar datos desde la API; el comportamiento es ahora consistente.</t>
+  </si>
+  <si>
+    <t>Se añadió validación obligatoria en frontend y backend.</t>
+  </si>
+  <si>
+    <t>El sistema permitía enviar sugerencias sin validar el campo correo electrónico, generando registros incompletos.</t>
+  </si>
+  <si>
+    <t>Algunas recomendaciones generadas aparecían vacías o con texto genérico sin valor para el usuario.</t>
+  </si>
+  <si>
+    <t>Los mensajes de error del login revelaban demasiada información (“usuario no existe” o “contraseña incorrecta”).</t>
+  </si>
+  <si>
+    <t>Las consultas del historial emocional eran lentas para usuarios con muchos registros.</t>
+  </si>
+  <si>
+    <t>Seguridad / Interfaz</t>
+  </si>
+  <si>
+    <t>Se identificó necesidad de agregar índices en user_id y date; mejora programada para el próximo sprint..</t>
+  </si>
+  <si>
+    <t>Se unificó la respuesta del backend a un mensaje genérico para no revelar información sensible.</t>
+  </si>
+  <si>
+    <t>Se ajustó el modelo y mensajes por defecto; falta nuevo dataset para mejorar precisión.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +290,12 @@
       <i/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -259,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -274,14 +406,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -292,14 +424,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -329,7 +470,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>394291</xdr:colOff>
+      <xdr:colOff>144259</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
@@ -685,287 +826,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:J51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.86328125" style="2" customWidth="1"/>
-    <col min="2" max="4" width="9.3984375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.86328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="69.1328125" style="2" customWidth="1"/>
-    <col min="7" max="9" width="15.265625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="34.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.3984375" style="2"/>
+    <col min="1" max="1" width="8.5703125" style="2" customWidth="1"/>
+    <col min="2" max="3" width="9.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="69.140625" style="2" customWidth="1"/>
+    <col min="7" max="9" width="15.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="34.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="F2" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
       <c r="D4" s="13"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="16"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="E4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="E5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="11" t="s">
+      <c r="E6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="13"/>
+    </row>
+    <row r="10" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="18">
+        <v>45935</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="16"/>
-    </row>
-    <row r="9" spans="1:10" s="7" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A9" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="I11" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="18">
+        <v>45938</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="I12" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="18">
+        <v>45940</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="18">
+        <v>45945</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="18">
+        <v>45948</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="18">
+        <v>45950</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="18">
+        <v>45952</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="18">
+        <v>45955</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="18">
+        <v>45958</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -977,7 +1274,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -989,7 +1286,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1001,7 +1298,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1013,7 +1310,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1025,7 +1322,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1037,7 +1334,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1049,7 +1346,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1061,7 +1358,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -1073,7 +1370,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1085,7 +1382,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1097,7 +1394,7 @@
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1109,7 +1406,7 @@
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1121,7 +1418,7 @@
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1133,7 +1430,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1145,7 +1442,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1157,7 +1454,7 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1169,7 +1466,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -1181,7 +1478,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -1193,7 +1490,7 @@
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -1205,7 +1502,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1217,7 +1514,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1229,7 +1526,7 @@
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1241,7 +1538,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1253,7 +1550,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1265,7 +1562,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -1277,7 +1574,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1295,29 +1592,24 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
     <mergeCell ref="E4:I4"/>
     <mergeCell ref="E5:I5"/>
     <mergeCell ref="E6:I6"/>
-    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="E8:I8"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Hoja2!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>E52:E53</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
-          <x14:formula1>
-            <xm:f>Hoja2!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>F52:G53</xm:sqref>
+          <xm:sqref>E52:G53</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1328,116 +1620,116 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C8" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" s="1" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
